--- a/packages/calculators/src/modules/test/11-wastewater.xlsx
+++ b/packages/calculators/src/modules/test/11-wastewater.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mackcheesman/Desktop/Work/EAP/Code/emissions-calculators/packages/calculators/src/modules/test/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mackcheesman/Desktop/Work/EAP/Code/emissions-calculators-internal/packages/calculators/src/modules/test/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD6A69E8-7FBF-B24A-9A69-8910D0934DF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05701E81-48AA-EE4B-93F7-2376216C08ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="11.1" sheetId="1" r:id="rId1"/>
+    <sheet name="11.1.1" sheetId="1" r:id="rId1"/>
+    <sheet name="11.1.2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,13 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="41">
-  <si>
-    <t>((Wt * (CODin * (1 - Fsludge ) - CODout) * CFww,t * EFww) + (Wt * (CODin * (Fsludge - Fremoved)) * CFsludge,t * EFsludge) - (6.784 * (10 ** -4) * (Qcap + Qflared + Qout)) +(Qflared * (ECflared * EFflared,CH4))) / 1000</t>
-  </si>
-  <si>
-    <t>(Qflared / 1000) * (ECflared * EFflared,N2O)</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="53">
   <si>
     <t>input</t>
   </si>
@@ -47,9 +42,6 @@
     <t>constant</t>
   </si>
   <si>
-    <t>expression</t>
-  </si>
-  <si>
     <t>Wt</t>
   </si>
   <si>
@@ -131,9 +123,6 @@
     <t>kg CH4/kg COD</t>
   </si>
   <si>
-    <t>m^3 CH4</t>
-  </si>
-  <si>
     <t>m^3 wastewater</t>
   </si>
   <si>
@@ -146,22 +135,74 @@
     <t>t CH4</t>
   </si>
   <si>
-    <t>kg N2O/GJ</t>
-  </si>
-  <si>
     <t>t N2O</t>
   </si>
   <si>
     <t>Method 1</t>
   </si>
   <si>
-    <t>NOTE: I think the formula might be wrong about 6.784 * 10^-4, should be ^-1 ?</t>
+    <t>c</t>
+  </si>
+  <si>
+    <t>Commodity Type c</t>
+  </si>
+  <si>
+    <t>CODin,c</t>
+  </si>
+  <si>
+    <t>Rc</t>
+  </si>
+  <si>
+    <t>Dairy products</t>
+  </si>
+  <si>
+    <t>Pulp, paper and paperboard</t>
+  </si>
+  <si>
+    <t>Meat and poultry</t>
+  </si>
+  <si>
+    <t>Raw sugar</t>
+  </si>
+  <si>
+    <t>Beer</t>
+  </si>
+  <si>
+    <t>Wine and other alcoholic beverages</t>
+  </si>
+  <si>
+    <t>Fruit</t>
+  </si>
+  <si>
+    <t>Vegetables</t>
+  </si>
+  <si>
+    <t>Qgen</t>
+  </si>
+  <si>
+    <t>GWPCH4</t>
+  </si>
+  <si>
+    <t>METHANE_DENSITY</t>
+  </si>
+  <si>
+    <t>GWPN2O</t>
+  </si>
+  <si>
+    <t>Had to remove GWP here?</t>
+  </si>
+  <si>
+    <t>Rc &gt; 0.75</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.0000000000"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
+  </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
@@ -171,7 +212,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -190,6 +231,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -203,10 +250,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -541,665 +591,3025 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A4:Z18"/>
+  <dimension ref="A5:X33"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="18" max="18" width="17" customWidth="1"/>
+    <col min="18" max="18" width="24.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="P4" t="s">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="L6" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>0</v>
+      </c>
+      <c r="C7" t="s">
+        <v>0</v>
+      </c>
+      <c r="D7" t="s">
+        <v>0</v>
+      </c>
+      <c r="E7" t="s">
+        <v>0</v>
+      </c>
+      <c r="F7" t="s">
+        <v>0</v>
+      </c>
+      <c r="G7" t="s">
+        <v>1</v>
+      </c>
+      <c r="H7" t="s">
+        <v>1</v>
+      </c>
+      <c r="I7" t="s">
+        <v>0</v>
+      </c>
+      <c r="J7" t="s">
+        <v>1</v>
+      </c>
+      <c r="K7" t="s">
+        <v>1</v>
+      </c>
+      <c r="N7" t="s">
+        <v>1</v>
+      </c>
+      <c r="O7" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="V8" t="s">
+        <v>49</v>
+      </c>
+      <c r="W8">
+        <f>6.784*10^-4</f>
+        <v>6.7840000000000001E-4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="C9" t="s">
+        <v>29</v>
+      </c>
+      <c r="D9" t="s">
+        <v>27</v>
+      </c>
+      <c r="F9" t="s">
+        <v>27</v>
+      </c>
+      <c r="H9" t="s">
+        <v>28</v>
+      </c>
+      <c r="K9" t="s">
+        <v>28</v>
+      </c>
+      <c r="L9" t="s">
+        <v>32</v>
+      </c>
+      <c r="N9" t="s">
+        <v>30</v>
+      </c>
+      <c r="O9" t="s">
+        <v>31</v>
+      </c>
+      <c r="P9" t="s">
+        <v>32</v>
+      </c>
+      <c r="R9" t="s">
+        <v>33</v>
+      </c>
+      <c r="V9" t="s">
+        <v>7</v>
+      </c>
+      <c r="W9">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L10" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="N10" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="O10" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="P10" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q10" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="R10" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="V10" t="s">
+        <v>10</v>
+      </c>
+      <c r="W10">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" t="s">
+        <v>39</v>
+      </c>
+      <c r="C11">
+        <v>2350000</v>
+      </c>
+      <c r="D11">
+        <f t="shared" ref="D11:D26" si="0">_xlfn.XLOOKUP(B11,$V$26:$V$33, $W$26:$W$33)</f>
+        <v>0.9</v>
+      </c>
+      <c r="E11">
+        <f t="shared" ref="E11:E26" si="1">$W$14</f>
+        <v>0.15</v>
+      </c>
+      <c r="F11">
+        <f>D11*0.08</f>
+        <v>7.2000000000000008E-2</v>
+      </c>
+      <c r="G11">
+        <f t="shared" ref="G11:G26" si="2">_xlfn.XLOOKUP(A11,$V$19:$V$23, $W$19:$W$23)</f>
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <f t="shared" ref="H11:H26" si="3">$W$9</f>
+        <v>0.25</v>
+      </c>
+      <c r="I11">
+        <v>0.2</v>
+      </c>
+      <c r="J11">
+        <f t="shared" ref="J11:J26" si="4">_xlfn.XLOOKUP(A11,$V$19:$V$23, $X$19:$X$23)</f>
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <f t="shared" ref="K11:K26" si="5">$W$10</f>
+        <v>0.25</v>
+      </c>
+      <c r="L11">
+        <f>((C11*(D11*(1-E11)-F11)*G11*H11)+(C11*(D11*(E11-I11))*J11*K11))*(1/1000)</f>
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <f t="shared" ref="M11:M26" si="6">_xlfn.XLOOKUP(B11,$V$26:$V$33, $X$26:$X$33)</f>
+        <v>0.39800000000000002</v>
+      </c>
+      <c r="N11">
+        <f t="shared" ref="N11:N26" si="7">$W$11</f>
+        <v>3.7699999999999997E-2</v>
+      </c>
+      <c r="O11">
+        <f t="shared" ref="O11:O26" si="8">$W$12</f>
+        <v>0.2286</v>
+      </c>
+      <c r="P11">
+        <f>L11*(1-M11+M11*((N11*O11)/($W$8*1*1000)))</f>
+        <v>0</v>
+      </c>
+      <c r="Q11">
+        <f>$W$13</f>
+        <v>1.132E-4</v>
+      </c>
+      <c r="R11" s="4">
+        <f>(M11*L11)/($W$8*1*1000)*(N11*Q11)</f>
+        <v>0</v>
+      </c>
+      <c r="V11" t="s">
+        <v>14</v>
+      </c>
+      <c r="W11">
+        <v>3.7699999999999997E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" t="s">
         <v>40</v>
+      </c>
+      <c r="C12">
+        <v>2350000</v>
+      </c>
+      <c r="D12">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+      <c r="E12">
+        <f t="shared" si="1"/>
+        <v>0.15</v>
+      </c>
+      <c r="F12">
+        <f t="shared" ref="F12:F26" si="9">D12*0.08</f>
+        <v>3.2000000000000001E-2</v>
+      </c>
+      <c r="G12">
+        <f t="shared" si="2"/>
+        <v>0.3</v>
+      </c>
+      <c r="H12">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="I12">
+        <v>0.05</v>
+      </c>
+      <c r="J12">
+        <f t="shared" si="4"/>
+        <v>0.3</v>
+      </c>
+      <c r="K12">
+        <f t="shared" si="5"/>
+        <v>0.25</v>
+      </c>
+      <c r="L12">
+        <f t="shared" ref="L12:L26" si="10">((C12*(D12*(1-E12)-F12)*G12*H12)+(C12*(D12*(E12-I12))*J12*K12))*(1/1000)</f>
+        <v>61.335000000000008</v>
+      </c>
+      <c r="M12">
+        <f t="shared" si="6"/>
+        <v>0.54700000000000004</v>
+      </c>
+      <c r="N12">
+        <f t="shared" si="7"/>
+        <v>3.7699999999999997E-2</v>
+      </c>
+      <c r="O12">
+        <f t="shared" si="8"/>
+        <v>0.2286</v>
+      </c>
+      <c r="P12">
+        <f t="shared" ref="P12:P26" si="11">L12*(1-M12+M12*((N12*O12)/($W$8*1*1000)))</f>
+        <v>28.210968727098908</v>
+      </c>
+      <c r="Q12">
+        <f t="shared" ref="Q12:Q26" si="12">$W$13</f>
+        <v>1.132E-4</v>
+      </c>
+      <c r="R12" s="4">
+        <f t="shared" ref="R12:R26" si="13">(M12*L12)/($W$8*1*1000)*(N12*Q12)</f>
+        <v>2.1105596634994104E-4</v>
+      </c>
+      <c r="V12" t="s">
+        <v>15</v>
+      </c>
+      <c r="W12">
+        <v>0.2286</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13" t="s">
+        <v>41</v>
+      </c>
+      <c r="C13">
+        <v>2350000</v>
+      </c>
+      <c r="D13">
+        <f t="shared" si="0"/>
+        <v>6.1</v>
+      </c>
+      <c r="E13">
+        <f t="shared" si="1"/>
+        <v>0.15</v>
+      </c>
+      <c r="F13">
+        <f t="shared" si="9"/>
+        <v>0.48799999999999999</v>
+      </c>
+      <c r="G13">
+        <f t="shared" si="2"/>
+        <v>0.8</v>
+      </c>
+      <c r="H13">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="I13">
+        <v>0.2</v>
+      </c>
+      <c r="J13">
+        <f t="shared" si="4"/>
+        <v>0.8</v>
+      </c>
+      <c r="K13">
+        <f t="shared" si="5"/>
+        <v>0.25</v>
+      </c>
+      <c r="L13">
+        <f t="shared" si="10"/>
+        <v>2064.2399999999998</v>
+      </c>
+      <c r="M13">
+        <f t="shared" si="6"/>
+        <v>0.34799999999999998</v>
+      </c>
+      <c r="N13">
+        <f t="shared" si="7"/>
+        <v>3.7699999999999997E-2</v>
+      </c>
+      <c r="O13">
+        <f t="shared" si="8"/>
+        <v>0.2286</v>
+      </c>
+      <c r="P13">
+        <f t="shared" si="11"/>
+        <v>1355.0102847016133</v>
+      </c>
+      <c r="Q13">
+        <f t="shared" si="12"/>
+        <v>1.132E-4</v>
+      </c>
+      <c r="R13" s="4">
+        <f t="shared" si="13"/>
+        <v>4.518989904735848E-3</v>
+      </c>
+      <c r="V13" t="s">
+        <v>17</v>
+      </c>
+      <c r="W13">
+        <v>1.132E-4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" t="s">
+        <v>42</v>
+      </c>
+      <c r="C14">
+        <v>2350000</v>
+      </c>
+      <c r="D14">
+        <f t="shared" si="0"/>
+        <v>3.8</v>
+      </c>
+      <c r="E14">
+        <f t="shared" si="1"/>
+        <v>0.15</v>
+      </c>
+      <c r="F14">
+        <f t="shared" si="9"/>
+        <v>0.30399999999999999</v>
+      </c>
+      <c r="G14">
+        <f t="shared" si="2"/>
+        <v>0.2</v>
+      </c>
+      <c r="H14">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="I14">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="J14">
+        <f t="shared" si="4"/>
+        <v>0.2</v>
+      </c>
+      <c r="K14">
+        <f t="shared" si="5"/>
+        <v>0.25</v>
+      </c>
+      <c r="L14">
+        <f t="shared" si="10"/>
+        <v>379.52500000000003</v>
+      </c>
+      <c r="M14">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="N14">
+        <f t="shared" si="7"/>
+        <v>3.7699999999999997E-2</v>
+      </c>
+      <c r="O14">
+        <f t="shared" si="8"/>
+        <v>0.2286</v>
+      </c>
+      <c r="P14">
+        <f t="shared" si="11"/>
+        <v>379.52500000000003</v>
+      </c>
+      <c r="Q14">
+        <f t="shared" si="12"/>
+        <v>1.132E-4</v>
+      </c>
+      <c r="R14" s="4">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="V14" t="s">
+        <v>4</v>
+      </c>
+      <c r="W14">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>24</v>
+      </c>
+      <c r="B15" t="s">
+        <v>43</v>
+      </c>
+      <c r="C15">
+        <v>2350000</v>
+      </c>
+      <c r="D15">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="E15">
+        <f t="shared" si="1"/>
+        <v>0.15</v>
+      </c>
+      <c r="F15">
+        <f t="shared" si="9"/>
+        <v>0.48</v>
+      </c>
+      <c r="G15">
+        <f t="shared" si="2"/>
+        <v>0.8</v>
+      </c>
+      <c r="H15">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="I15">
+        <v>0.1</v>
+      </c>
+      <c r="J15">
+        <f t="shared" si="4"/>
+        <v>0.8</v>
+      </c>
+      <c r="K15">
+        <f t="shared" si="5"/>
+        <v>0.25</v>
+      </c>
+      <c r="L15">
+        <f t="shared" si="10"/>
+        <v>2312.3999999999996</v>
+      </c>
+      <c r="M15">
+        <f t="shared" si="6"/>
+        <v>0.72299999999999998</v>
+      </c>
+      <c r="N15">
+        <f t="shared" si="7"/>
+        <v>3.7699999999999997E-2</v>
+      </c>
+      <c r="O15">
+        <f t="shared" si="8"/>
+        <v>0.2286</v>
+      </c>
+      <c r="P15">
+        <f t="shared" si="11"/>
+        <v>661.77374767680419</v>
+      </c>
+      <c r="Q15">
+        <f t="shared" si="12"/>
+        <v>1.132E-4</v>
+      </c>
+      <c r="R15" s="4">
+        <f t="shared" si="13"/>
+        <v>1.0517274177665091E-2</v>
+      </c>
+      <c r="V15" t="s">
+        <v>48</v>
+      </c>
+      <c r="W15">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>20</v>
+      </c>
+      <c r="B16" t="s">
+        <v>44</v>
+      </c>
+      <c r="C16">
+        <v>2350000</v>
+      </c>
+      <c r="D16">
+        <f t="shared" si="0"/>
+        <v>1.5</v>
+      </c>
+      <c r="E16">
+        <f t="shared" si="1"/>
+        <v>0.15</v>
+      </c>
+      <c r="F16">
+        <f t="shared" si="9"/>
+        <v>0.12</v>
+      </c>
+      <c r="G16">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <f t="shared" si="5"/>
+        <v>0.25</v>
+      </c>
+      <c r="L16">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="M16">
+        <f t="shared" si="6"/>
+        <v>0.79600000000000004</v>
+      </c>
+      <c r="N16">
+        <f t="shared" si="7"/>
+        <v>3.7699999999999997E-2</v>
+      </c>
+      <c r="O16">
+        <f t="shared" si="8"/>
+        <v>0.2286</v>
+      </c>
+      <c r="P16">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="Q16">
+        <f t="shared" si="12"/>
+        <v>1.132E-4</v>
+      </c>
+      <c r="R16" s="4">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="V16" t="s">
+        <v>50</v>
+      </c>
+      <c r="W16">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="17" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>21</v>
+      </c>
+      <c r="B17" t="s">
+        <v>45</v>
+      </c>
+      <c r="C17">
+        <v>2350000</v>
+      </c>
+      <c r="D17">
+        <f t="shared" si="0"/>
+        <v>0.2</v>
+      </c>
+      <c r="E17">
+        <f t="shared" si="1"/>
+        <v>0.15</v>
+      </c>
+      <c r="F17">
+        <f t="shared" si="9"/>
+        <v>1.6E-2</v>
+      </c>
+      <c r="G17">
+        <f t="shared" si="2"/>
+        <v>0.3</v>
+      </c>
+      <c r="H17">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <f t="shared" si="4"/>
+        <v>0.3</v>
+      </c>
+      <c r="K17">
+        <f t="shared" si="5"/>
+        <v>0.25</v>
+      </c>
+      <c r="L17">
+        <f t="shared" si="10"/>
+        <v>32.430000000000007</v>
+      </c>
+      <c r="M17">
+        <f t="shared" si="6"/>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="N17">
+        <f t="shared" si="7"/>
+        <v>3.7699999999999997E-2</v>
+      </c>
+      <c r="O17">
+        <f t="shared" si="8"/>
+        <v>0.2286</v>
+      </c>
+      <c r="P17">
+        <f t="shared" si="11"/>
+        <v>32.269909912106435</v>
+      </c>
+      <c r="Q17">
+        <f t="shared" si="12"/>
+        <v>1.132E-4</v>
+      </c>
+      <c r="R17" s="4">
+        <f t="shared" si="13"/>
+        <v>1.0200439652122644E-6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>22</v>
+      </c>
+      <c r="B18" t="s">
+        <v>46</v>
+      </c>
+      <c r="C18">
+        <v>2350000</v>
+      </c>
+      <c r="D18">
+        <f t="shared" si="0"/>
+        <v>0.2</v>
+      </c>
+      <c r="E18">
+        <f t="shared" si="1"/>
+        <v>0.15</v>
+      </c>
+      <c r="F18">
+        <f t="shared" si="9"/>
+        <v>1.6E-2</v>
+      </c>
+      <c r="G18">
+        <f t="shared" si="2"/>
+        <v>0.8</v>
+      </c>
+      <c r="H18">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <f t="shared" si="4"/>
+        <v>0.8</v>
+      </c>
+      <c r="K18">
+        <f t="shared" si="5"/>
+        <v>0.25</v>
+      </c>
+      <c r="L18">
+        <f t="shared" si="10"/>
+        <v>86.480000000000018</v>
+      </c>
+      <c r="M18">
+        <f t="shared" si="6"/>
+        <v>0.06</v>
+      </c>
+      <c r="N18">
+        <f t="shared" si="7"/>
+        <v>3.7699999999999997E-2</v>
+      </c>
+      <c r="O18">
+        <f t="shared" si="8"/>
+        <v>0.2286</v>
+      </c>
+      <c r="P18">
+        <f t="shared" si="11"/>
+        <v>81.357117187405677</v>
+      </c>
+      <c r="Q18">
+        <f t="shared" si="12"/>
+        <v>1.132E-4</v>
+      </c>
+      <c r="R18" s="4">
+        <f t="shared" si="13"/>
+        <v>3.2641406886792456E-5</v>
+      </c>
+      <c r="V18" t="s">
+        <v>19</v>
+      </c>
+      <c r="W18" t="s">
+        <v>6</v>
+      </c>
+      <c r="X18" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="19" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>23</v>
+      </c>
+      <c r="B19" t="s">
+        <v>39</v>
+      </c>
+      <c r="C19">
+        <v>2350000</v>
+      </c>
+      <c r="D19">
+        <f t="shared" si="0"/>
+        <v>0.9</v>
+      </c>
+      <c r="E19">
+        <f t="shared" si="1"/>
+        <v>0.15</v>
+      </c>
+      <c r="F19">
+        <f t="shared" si="9"/>
+        <v>7.2000000000000008E-2</v>
+      </c>
+      <c r="G19">
+        <f t="shared" si="2"/>
+        <v>0.2</v>
+      </c>
+      <c r="H19">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <f t="shared" si="4"/>
+        <v>0.2</v>
+      </c>
+      <c r="K19">
+        <f t="shared" si="5"/>
+        <v>0.25</v>
+      </c>
+      <c r="L19">
+        <f t="shared" si="10"/>
+        <v>97.29000000000002</v>
+      </c>
+      <c r="M19">
+        <f t="shared" si="6"/>
+        <v>0.39800000000000002</v>
+      </c>
+      <c r="N19">
+        <f t="shared" si="7"/>
+        <v>3.7699999999999997E-2</v>
+      </c>
+      <c r="O19">
+        <f t="shared" si="8"/>
+        <v>0.2286</v>
+      </c>
+      <c r="P19">
+        <f t="shared" si="11"/>
+        <v>59.06048701101475</v>
+      </c>
+      <c r="Q19">
+        <f t="shared" si="12"/>
+        <v>1.132E-4</v>
+      </c>
+      <c r="R19" s="4">
+        <f t="shared" si="13"/>
+        <v>2.4358649889268875E-4</v>
+      </c>
+      <c r="V19" t="s">
+        <v>20</v>
+      </c>
+      <c r="W19">
+        <v>0</v>
+      </c>
+      <c r="X19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>24</v>
+      </c>
+      <c r="B20" t="s">
+        <v>40</v>
+      </c>
+      <c r="C20">
+        <v>2350000</v>
+      </c>
+      <c r="D20">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+      <c r="E20">
+        <f t="shared" si="1"/>
+        <v>0.15</v>
+      </c>
+      <c r="F20">
+        <f t="shared" si="9"/>
+        <v>3.2000000000000001E-2</v>
+      </c>
+      <c r="G20">
+        <f t="shared" si="2"/>
+        <v>0.8</v>
+      </c>
+      <c r="H20">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <f t="shared" si="4"/>
+        <v>0.8</v>
+      </c>
+      <c r="K20">
+        <f t="shared" si="5"/>
+        <v>0.25</v>
+      </c>
+      <c r="L20">
+        <f t="shared" si="10"/>
+        <v>172.96000000000004</v>
+      </c>
+      <c r="M20">
+        <f t="shared" si="6"/>
+        <v>0.54700000000000004</v>
+      </c>
+      <c r="N20">
+        <f t="shared" si="7"/>
+        <v>3.7699999999999997E-2</v>
+      </c>
+      <c r="O20">
+        <f t="shared" si="8"/>
+        <v>0.2286</v>
+      </c>
+      <c r="P20">
+        <f t="shared" si="11"/>
+        <v>79.552770050363222</v>
+      </c>
+      <c r="Q20">
+        <f t="shared" si="12"/>
+        <v>1.132E-4</v>
+      </c>
+      <c r="R20" s="4">
+        <f t="shared" si="13"/>
+        <v>5.9516165223584929E-4</v>
+      </c>
+      <c r="V20" t="s">
+        <v>21</v>
+      </c>
+      <c r="W20">
+        <v>0.3</v>
+      </c>
+      <c r="X20">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>41</v>
+      </c>
+      <c r="C21">
+        <v>2350000</v>
+      </c>
+      <c r="D21">
+        <f t="shared" si="0"/>
+        <v>6.1</v>
+      </c>
+      <c r="E21">
+        <f t="shared" si="1"/>
+        <v>0.15</v>
+      </c>
+      <c r="F21">
+        <f t="shared" si="9"/>
+        <v>0.48799999999999999</v>
+      </c>
+      <c r="G21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <f t="shared" si="5"/>
+        <v>0.25</v>
+      </c>
+      <c r="L21">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="M21">
+        <f t="shared" si="6"/>
+        <v>0.34799999999999998</v>
+      </c>
+      <c r="N21">
+        <f t="shared" si="7"/>
+        <v>3.7699999999999997E-2</v>
+      </c>
+      <c r="O21">
+        <f t="shared" si="8"/>
+        <v>0.2286</v>
+      </c>
+      <c r="P21">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="Q21">
+        <f t="shared" si="12"/>
+        <v>1.132E-4</v>
+      </c>
+      <c r="R21" s="4">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="V21" t="s">
+        <v>22</v>
+      </c>
+      <c r="W21">
+        <v>0.8</v>
+      </c>
+      <c r="X21">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="22" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>42</v>
+      </c>
+      <c r="C22">
+        <v>2350000</v>
+      </c>
+      <c r="D22">
+        <f t="shared" si="0"/>
+        <v>3.8</v>
+      </c>
+      <c r="E22">
+        <f t="shared" si="1"/>
+        <v>0.15</v>
+      </c>
+      <c r="F22">
+        <f t="shared" si="9"/>
+        <v>0.30399999999999999</v>
+      </c>
+      <c r="G22">
+        <f t="shared" si="2"/>
+        <v>0.3</v>
+      </c>
+      <c r="H22">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <f t="shared" si="4"/>
+        <v>0.3</v>
+      </c>
+      <c r="K22">
+        <f t="shared" si="5"/>
+        <v>0.25</v>
+      </c>
+      <c r="L22">
+        <f t="shared" si="10"/>
+        <v>616.16999999999996</v>
+      </c>
+      <c r="M22">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="N22">
+        <f t="shared" si="7"/>
+        <v>3.7699999999999997E-2</v>
+      </c>
+      <c r="O22">
+        <f t="shared" si="8"/>
+        <v>0.2286</v>
+      </c>
+      <c r="P22">
+        <f t="shared" si="11"/>
+        <v>616.16999999999996</v>
+      </c>
+      <c r="Q22">
+        <f t="shared" si="12"/>
+        <v>1.132E-4</v>
+      </c>
+      <c r="R22" s="4">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="V22" t="s">
+        <v>23</v>
+      </c>
+      <c r="W22">
+        <v>0.2</v>
+      </c>
+      <c r="X22">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>43</v>
+      </c>
+      <c r="C23">
+        <v>2350000</v>
+      </c>
+      <c r="D23">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="E23">
+        <f t="shared" si="1"/>
+        <v>0.15</v>
+      </c>
+      <c r="F23">
+        <f t="shared" si="9"/>
+        <v>0.48</v>
+      </c>
+      <c r="G23">
+        <f t="shared" si="2"/>
+        <v>0.8</v>
+      </c>
+      <c r="H23">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <f t="shared" si="4"/>
+        <v>0.8</v>
+      </c>
+      <c r="K23">
+        <f t="shared" si="5"/>
+        <v>0.25</v>
+      </c>
+      <c r="L23">
+        <f t="shared" si="10"/>
+        <v>2594.3999999999996</v>
+      </c>
+      <c r="M23">
+        <f t="shared" si="6"/>
+        <v>0.72299999999999998</v>
+      </c>
+      <c r="N23">
+        <f t="shared" si="7"/>
+        <v>3.7699999999999997E-2</v>
+      </c>
+      <c r="O23">
+        <f t="shared" si="8"/>
+        <v>0.2286</v>
+      </c>
+      <c r="P23">
+        <f t="shared" si="11"/>
+        <v>742.47786324714616</v>
+      </c>
+      <c r="Q23">
+        <f t="shared" si="12"/>
+        <v>1.132E-4</v>
+      </c>
+      <c r="R23" s="4">
+        <f t="shared" si="13"/>
+        <v>1.179986858957547E-2</v>
+      </c>
+      <c r="V23" t="s">
+        <v>24</v>
+      </c>
+      <c r="W23">
+        <v>0.8</v>
+      </c>
+      <c r="X23">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="24" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>44</v>
+      </c>
+      <c r="C24">
+        <v>2350000</v>
+      </c>
+      <c r="D24">
+        <f t="shared" si="0"/>
+        <v>1.5</v>
+      </c>
+      <c r="E24">
+        <f t="shared" si="1"/>
+        <v>0.15</v>
+      </c>
+      <c r="F24">
+        <f t="shared" si="9"/>
+        <v>0.12</v>
+      </c>
+      <c r="G24">
+        <f t="shared" si="2"/>
+        <v>0.2</v>
+      </c>
+      <c r="H24">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <f t="shared" si="4"/>
+        <v>0.2</v>
+      </c>
+      <c r="K24">
+        <f t="shared" si="5"/>
+        <v>0.25</v>
+      </c>
+      <c r="L24">
+        <f t="shared" si="10"/>
+        <v>162.14999999999998</v>
+      </c>
+      <c r="M24">
+        <f t="shared" si="6"/>
+        <v>0.79600000000000004</v>
+      </c>
+      <c r="N24">
+        <f t="shared" si="7"/>
+        <v>3.7699999999999997E-2</v>
+      </c>
+      <c r="O24">
+        <f t="shared" si="8"/>
+        <v>0.2286</v>
+      </c>
+      <c r="P24">
+        <f t="shared" si="11"/>
+        <v>34.718290036715793</v>
+      </c>
+      <c r="Q24">
+        <f t="shared" si="12"/>
+        <v>1.132E-4</v>
+      </c>
+      <c r="R24" s="4">
+        <f t="shared" si="13"/>
+        <v>8.1195499630896213E-4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>45</v>
+      </c>
+      <c r="C25">
+        <v>2350000</v>
+      </c>
+      <c r="D25">
+        <f t="shared" si="0"/>
+        <v>0.2</v>
+      </c>
+      <c r="E25">
+        <f t="shared" si="1"/>
+        <v>0.15</v>
+      </c>
+      <c r="F25">
+        <f t="shared" si="9"/>
+        <v>1.6E-2</v>
+      </c>
+      <c r="G25">
+        <f t="shared" si="2"/>
+        <v>0.8</v>
+      </c>
+      <c r="H25">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <f t="shared" si="4"/>
+        <v>0.8</v>
+      </c>
+      <c r="K25">
+        <f t="shared" si="5"/>
+        <v>0.25</v>
+      </c>
+      <c r="L25">
+        <f t="shared" si="10"/>
+        <v>86.480000000000018</v>
+      </c>
+      <c r="M25">
+        <f t="shared" si="6"/>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="N25">
+        <f t="shared" si="7"/>
+        <v>3.7699999999999997E-2</v>
+      </c>
+      <c r="O25">
+        <f t="shared" si="8"/>
+        <v>0.2286</v>
+      </c>
+      <c r="P25">
+        <f t="shared" si="11"/>
+        <v>86.053093098950498</v>
+      </c>
+      <c r="Q25">
+        <f t="shared" si="12"/>
+        <v>1.132E-4</v>
+      </c>
+      <c r="R25" s="4">
+        <f t="shared" si="13"/>
+        <v>2.7201172405660381E-6</v>
+      </c>
+      <c r="V25" t="s">
+        <v>36</v>
+      </c>
+      <c r="W25" t="s">
+        <v>37</v>
+      </c>
+      <c r="X25" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="26" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>20</v>
+      </c>
+      <c r="B26" t="s">
+        <v>46</v>
+      </c>
+      <c r="C26">
+        <v>2350000</v>
+      </c>
+      <c r="D26">
+        <f t="shared" si="0"/>
+        <v>0.2</v>
+      </c>
+      <c r="E26">
+        <f t="shared" si="1"/>
+        <v>0.15</v>
+      </c>
+      <c r="F26">
+        <f t="shared" si="9"/>
+        <v>1.6E-2</v>
+      </c>
+      <c r="G26">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <f t="shared" si="5"/>
+        <v>0.25</v>
+      </c>
+      <c r="L26">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="M26">
+        <f t="shared" si="6"/>
+        <v>0.06</v>
+      </c>
+      <c r="N26">
+        <f t="shared" si="7"/>
+        <v>3.7699999999999997E-2</v>
+      </c>
+      <c r="O26">
+        <f t="shared" si="8"/>
+        <v>0.2286</v>
+      </c>
+      <c r="P26">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="Q26">
+        <f t="shared" si="12"/>
+        <v>1.132E-4</v>
+      </c>
+      <c r="R26" s="4">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="V26" t="s">
+        <v>39</v>
+      </c>
+      <c r="W26">
+        <v>0.9</v>
+      </c>
+      <c r="X26">
+        <v>0.39800000000000002</v>
+      </c>
+    </row>
+    <row r="27" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="V27" t="s">
+        <v>40</v>
+      </c>
+      <c r="W27">
+        <v>0.4</v>
+      </c>
+      <c r="X27">
+        <v>0.54700000000000004</v>
+      </c>
+    </row>
+    <row r="28" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="V28" t="s">
+        <v>41</v>
+      </c>
+      <c r="W28">
+        <v>6.1</v>
+      </c>
+      <c r="X28">
+        <v>0.34799999999999998</v>
+      </c>
+    </row>
+    <row r="29" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="V29" t="s">
+        <v>42</v>
+      </c>
+      <c r="W29">
+        <v>3.8</v>
+      </c>
+      <c r="X29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="V30" t="s">
+        <v>43</v>
+      </c>
+      <c r="W30">
+        <v>6</v>
+      </c>
+      <c r="X30">
+        <v>0.72299999999999998</v>
+      </c>
+    </row>
+    <row r="31" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="V31" t="s">
+        <v>44</v>
+      </c>
+      <c r="W31">
+        <v>1.5</v>
+      </c>
+      <c r="X31">
+        <v>0.79600000000000004</v>
+      </c>
+    </row>
+    <row r="32" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="V32" t="s">
+        <v>45</v>
+      </c>
+      <c r="W32">
+        <v>0.2</v>
+      </c>
+      <c r="X32">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="33" spans="22:24" x14ac:dyDescent="0.2">
+      <c r="V33" t="s">
+        <v>46</v>
+      </c>
+      <c r="W33">
+        <v>0.2</v>
+      </c>
+      <c r="X33">
+        <v>0.06</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A41F606-F5DD-FC49-8A3E-E995FC64E994}">
+  <dimension ref="A3:AA33"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="12" max="12" width="22.1640625" customWidth="1"/>
+    <col min="16" max="16" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="24.33203125" customWidth="1"/>
+    <col min="21" max="21" width="19" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="F3">
+        <f>(D12*(1-E12)-F12)</f>
+        <v>0.32800000000000007</v>
+      </c>
+      <c r="G3">
+        <f>F3*C12*G12*H12</f>
+        <v>57810.000000000007</v>
+      </c>
+      <c r="H3">
+        <f>(C12*(D12*(E12-I12))*J12*K12)</f>
+        <v>3525.0000000000005</v>
+      </c>
+      <c r="I3">
+        <f>(G3+H3)/1000</f>
+        <v>61.335000000000008</v>
       </c>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>39</v>
-      </c>
-      <c r="P5" t="s">
-        <v>0</v>
-      </c>
-      <c r="R5" t="s">
-        <v>1</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="B6">
-        <v>164</v>
-      </c>
-      <c r="C6">
-        <v>165</v>
-      </c>
-      <c r="D6">
-        <v>166</v>
-      </c>
-      <c r="E6">
-        <v>168</v>
-      </c>
-      <c r="F6">
-        <v>169</v>
-      </c>
-      <c r="G6">
-        <v>171</v>
-      </c>
-      <c r="H6">
-        <v>172</v>
-      </c>
-      <c r="I6">
-        <v>174</v>
-      </c>
-      <c r="J6">
-        <v>176</v>
-      </c>
-      <c r="K6">
-        <v>177</v>
-      </c>
-      <c r="L6">
-        <v>179</v>
-      </c>
-      <c r="M6">
-        <v>181</v>
-      </c>
-      <c r="N6">
-        <v>183</v>
-      </c>
-      <c r="O6">
-        <v>184</v>
-      </c>
-      <c r="P6">
-        <v>161</v>
-      </c>
-      <c r="Q6">
-        <v>198</v>
-      </c>
-      <c r="R6">
-        <v>197</v>
+      <c r="L6" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>2</v>
-      </c>
-      <c r="B7" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C7" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D7" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E7" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F7" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G7" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H7" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I7" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J7" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K7" t="s">
-        <v>2</v>
-      </c>
-      <c r="L7" t="s">
-        <v>2</v>
-      </c>
-      <c r="M7" t="s">
-        <v>2</v>
-      </c>
-      <c r="N7" t="s">
-        <v>3</v>
-      </c>
-      <c r="O7" t="s">
-        <v>3</v>
-      </c>
-      <c r="P7" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Q7" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R7" t="s">
-        <v>4</v>
-      </c>
-      <c r="T7" t="s">
-        <v>10</v>
-      </c>
-      <c r="U7">
-        <v>0.25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="T8" t="s">
-        <v>13</v>
-      </c>
-      <c r="U8">
-        <v>0.25</v>
+      <c r="Y8" t="s">
+        <v>49</v>
+      </c>
+      <c r="Z8">
+        <f>6.784*10^-4</f>
+        <v>6.7840000000000001E-4</v>
       </c>
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="B9" t="s">
-        <v>33</v>
-      </c>
       <c r="C9" t="s">
-        <v>30</v>
-      </c>
-      <c r="E9" t="s">
-        <v>30</v>
-      </c>
-      <c r="G9" t="s">
-        <v>31</v>
-      </c>
-      <c r="J9" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="D9" t="s">
+        <v>27</v>
+      </c>
+      <c r="F9" t="s">
+        <v>27</v>
+      </c>
+      <c r="H9" t="s">
+        <v>28</v>
       </c>
       <c r="K9" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="L9" t="s">
         <v>32</v>
       </c>
-      <c r="M9" t="s">
+      <c r="Q9" t="s">
+        <v>30</v>
+      </c>
+      <c r="R9" t="s">
+        <v>31</v>
+      </c>
+      <c r="S9" t="s">
         <v>32</v>
       </c>
-      <c r="N9" t="s">
-        <v>34</v>
-      </c>
-      <c r="O9" t="s">
-        <v>35</v>
-      </c>
-      <c r="P9" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>37</v>
-      </c>
-      <c r="R9" t="s">
-        <v>38</v>
-      </c>
-      <c r="T9" t="s">
-        <v>17</v>
-      </c>
-      <c r="U9">
-        <v>3.7699999999999997E-2</v>
+      <c r="U9" t="s">
+        <v>33</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>7</v>
+      </c>
+      <c r="Z9">
+        <v>0.25</v>
       </c>
     </row>
     <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B10" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="H10" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="I10" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="J10" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G10" s="1" t="s">
+      <c r="K10" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="H10" s="1" t="s">
+      <c r="L10" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="M10" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="I10" s="1" t="s">
+      <c r="N10" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="J10" s="1" t="s">
+      <c r="O10" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="K10" s="1" t="s">
+      <c r="P10" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q10" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="L10" s="1" t="s">
+      <c r="R10" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="M10" s="1" t="s">
+      <c r="S10" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="N10" s="1" t="s">
+      <c r="T10" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="O10" s="1" t="s">
+      <c r="U10" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="P10" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q10" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="R10" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="T10" t="s">
-        <v>18</v>
-      </c>
-      <c r="U10">
-        <v>0.22889999999999999</v>
+      <c r="Y10" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z10">
+        <v>0.25</v>
       </c>
     </row>
     <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>23</v>
-      </c>
-      <c r="B11">
+        <v>20</v>
+      </c>
+      <c r="C11">
         <v>2350000</v>
       </c>
-      <c r="C11">
-        <v>6.1</v>
-      </c>
       <c r="D11">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="E11">
-        <v>2.1</v>
+        <v>0.15</v>
       </c>
       <c r="F11">
-        <f>_xlfn.XLOOKUP(A11,$T$14:$T$18, $U$14:$U$18)</f>
-        <v>0</v>
+        <v>7.2000000000000008E-2</v>
       </c>
       <c r="G11">
-        <f>$U$7</f>
-        <v>0.25</v>
+        <f t="shared" ref="G11:G26" si="0">_xlfn.XLOOKUP(A11,$Y$19:$Y$23, $Z$19:$Z$23)</f>
+        <v>0</v>
       </c>
       <c r="H11">
-        <v>0.2</v>
+        <f t="shared" ref="H11:H26" si="1">$Z$9</f>
+        <v>0.25</v>
       </c>
       <c r="I11">
-        <f>_xlfn.XLOOKUP(A11,$T$14:$T$18, $V$14:$V$18)</f>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="J11">
-        <f>$U$8</f>
-        <v>0.25</v>
+        <f t="shared" ref="J11:J26" si="2">_xlfn.XLOOKUP(A11,$Y$19:$Y$23, $AA$19:$AA$23)</f>
+        <v>0</v>
       </c>
       <c r="K11">
-        <v>0</v>
+        <f t="shared" ref="K11:K26" si="3">$Z$10</f>
+        <v>0.25</v>
       </c>
       <c r="L11">
+        <f>((C11*(D11*(1-E11)-F11)*G11*H11)+(C11*(D11*(E11-I11))*J11*K11))*(1/1000)</f>
         <v>0</v>
       </c>
       <c r="M11">
         <v>0</v>
       </c>
       <c r="N11">
-        <f>$U$9</f>
+        <v>0</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11" t="b">
+        <f>SUM(M11:O11)*$Z$8&gt;L11*0.75</f>
+        <v>0</v>
+      </c>
+      <c r="Q11">
+        <f t="shared" ref="Q11:Q26" si="4">$Z$11</f>
         <v>3.7699999999999997E-2</v>
       </c>
-      <c r="O11">
-        <f>$U$10</f>
-        <v>0.22889999999999999</v>
-      </c>
-      <c r="P11">
-        <f>((B11 * (C11 *(1 - D11) - E11 ) * F11 * G11) + (B11 * (C11 * (D11-H11)) * I11 * J11) - (6.784 * 10^-1 * (K11+L11+M11)) + (L11 * (N11 * O11)))/1000</f>
-        <v>0</v>
-      </c>
-      <c r="Q11">
-        <f>$U$11</f>
+      <c r="R11">
+        <f t="shared" ref="R11:R26" si="5">$Z$12</f>
+        <v>0.2286</v>
+      </c>
+      <c r="S11">
+        <f>IF(P11, SUM(M11:O11)/3 *$Z$8,L11-($Z$8*SUM(M11:O11))+(N11/(1000*1)*(Q11*R11)))</f>
+        <v>0</v>
+      </c>
+      <c r="T11">
+        <f t="shared" ref="T11:T26" si="6">$Z$13</f>
         <v>1.132E-4</v>
       </c>
-      <c r="R11">
-        <f>(L11 / 1000) * (N11 * Q11)</f>
-        <v>0</v>
-      </c>
-      <c r="T11" t="s">
-        <v>20</v>
-      </c>
-      <c r="U11">
-        <v>1.132E-4</v>
-      </c>
-      <c r="W11">
-        <f>(B11 * (C11 *(1 - D11) - E11 ) * F11 * G11)</f>
-        <v>0</v>
-      </c>
-      <c r="X11">
-        <f>(B11 * (C11 * (D11-H11)) * I11 * J11)</f>
-        <v>0</v>
-      </c>
-      <c r="Y11">
-        <f>((6.784 * 10^-1 * (K11+L11+M11)) )</f>
-        <v>0</v>
+      <c r="U11" s="4">
+        <f>N11/1000 * Q11*T11</f>
+        <v>0</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>14</v>
       </c>
       <c r="Z11">
-        <f>(L11 * (N11 * O11))</f>
-        <v>0</v>
+        <v>3.7699999999999997E-2</v>
       </c>
     </row>
     <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>24</v>
-      </c>
-      <c r="B12">
+        <v>21</v>
+      </c>
+      <c r="C12">
         <v>2350000</v>
       </c>
-      <c r="C12">
-        <v>3</v>
-      </c>
       <c r="D12">
+        <v>0.4</v>
+      </c>
+      <c r="E12">
+        <v>0.1</v>
+      </c>
+      <c r="F12">
+        <v>3.2000000000000001E-2</v>
+      </c>
+      <c r="G12">
+        <f t="shared" si="0"/>
         <v>0.3</v>
       </c>
-      <c r="E12">
-        <v>0.2</v>
-      </c>
-      <c r="F12">
-        <f t="shared" ref="F12:F15" si="0">_xlfn.XLOOKUP(A12,$T$14:$T$18, $U$14:$U$18)</f>
+      <c r="H12">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="I12">
+        <v>0.05</v>
+      </c>
+      <c r="J12">
+        <f t="shared" si="2"/>
         <v>0.3</v>
       </c>
-      <c r="G12">
-        <f t="shared" ref="G12:G15" si="1">$U$7</f>
-        <v>0.25</v>
-      </c>
-      <c r="H12">
-        <v>0.05</v>
-      </c>
-      <c r="I12">
-        <f t="shared" ref="I12:I15" si="2">_xlfn.XLOOKUP(A12,$T$14:$T$18, $V$14:$V$18)</f>
-        <v>0.3</v>
-      </c>
-      <c r="J12">
-        <f t="shared" ref="J12:J15" si="3">$U$8</f>
-        <v>0.25</v>
-      </c>
       <c r="K12">
-        <v>11000</v>
-      </c>
-      <c r="L12">
-        <v>2000</v>
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="L12" s="5">
+        <f>((C12*(D12*(1-E12)-F12)*G12*H12)+(C12*(D12*(E12-I12))*J12*K12))*(1/1000)</f>
+        <v>61.335000000000008</v>
       </c>
       <c r="M12">
-        <v>33000</v>
+        <v>30000</v>
       </c>
       <c r="N12">
-        <f t="shared" ref="N12:N15" si="4">$U$9</f>
+        <v>20000</v>
+      </c>
+      <c r="O12">
+        <v>20000</v>
+      </c>
+      <c r="P12" t="b">
+        <f t="shared" ref="P12:P26" si="7">SUM(M12:O12)*$Z$8&gt;L12*0.75</f>
+        <v>1</v>
+      </c>
+      <c r="Q12">
+        <f t="shared" si="4"/>
         <v>3.7699999999999997E-2</v>
       </c>
-      <c r="O12">
-        <f t="shared" ref="O12:O15" si="5">$U$10</f>
-        <v>0.22889999999999999</v>
-      </c>
-      <c r="P12">
-        <f t="shared" ref="P12:P15" si="6">((B12 * (C12 *(1 - D12) - E12 ) * F12 * G12) + (B12 * (C12 * (D12-H12)) * I12 * J12) - (6.784 * 10^-1 * (K12+L12+M12)) + (L12 * (N12 * O12)))/1000</f>
-        <v>435.87335905999993</v>
-      </c>
-      <c r="Q12">
-        <f t="shared" ref="Q12:Q15" si="7">$U$11</f>
+      <c r="R12">
+        <f t="shared" si="5"/>
+        <v>0.2286</v>
+      </c>
+      <c r="S12">
+        <f t="shared" ref="S12:S26" si="8">IF(P12, SUM(M12:O12)/3 *$Z$8,L12-($Z$8*SUM(M12:O12))+(N12/(1000*1)*(Q12*R12)))</f>
+        <v>15.829333333333333</v>
+      </c>
+      <c r="T12">
+        <f t="shared" si="6"/>
         <v>1.132E-4</v>
       </c>
-      <c r="R12">
-        <f t="shared" ref="R12:R15" si="8">(L12 / 1000) * (N12 * Q12)</f>
-        <v>8.5352799999999997E-6</v>
+      <c r="U12" s="4">
+        <f t="shared" ref="U12:U26" si="9">N12/1000 * Q12*T12</f>
+        <v>8.5352800000000007E-5</v>
+      </c>
+      <c r="Y12" t="s">
+        <v>15</v>
+      </c>
+      <c r="Z12">
+        <v>0.2286</v>
       </c>
     </row>
     <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>25</v>
-      </c>
-      <c r="B13">
+        <v>22</v>
+      </c>
+      <c r="C13">
         <v>2350000</v>
       </c>
-      <c r="C13">
-        <v>3.8</v>
-      </c>
       <c r="D13">
-        <v>0.6</v>
+        <v>6.1</v>
       </c>
       <c r="E13">
-        <v>3</v>
+        <v>0.15</v>
       </c>
       <c r="F13">
+        <v>0.48799999999999999</v>
+      </c>
+      <c r="G13">
         <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
-      <c r="G13">
+      <c r="H13">
         <f t="shared" si="1"/>
         <v>0.25</v>
       </c>
-      <c r="H13">
+      <c r="I13">
         <v>0.2</v>
       </c>
-      <c r="I13">
+      <c r="J13">
         <f t="shared" si="2"/>
         <v>0.8</v>
       </c>
-      <c r="J13">
+      <c r="K13">
         <f t="shared" si="3"/>
         <v>0.25</v>
       </c>
-      <c r="K13">
-        <v>1000</v>
-      </c>
       <c r="L13">
-        <v>500</v>
+        <f t="shared" ref="L13:L26" si="10">((C13*(D13*(1-E13)-F13)*G13*H13)+(C13*(D13*(E13-I13))*J13*K13))*(1/1000)</f>
+        <v>2064.2399999999998</v>
       </c>
       <c r="M13">
-        <v>300</v>
+        <v>20000</v>
       </c>
       <c r="N13">
+        <v>300000</v>
+      </c>
+      <c r="O13">
+        <v>20000</v>
+      </c>
+      <c r="P13" t="b">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="Q13">
         <f t="shared" si="4"/>
         <v>3.7699999999999997E-2</v>
       </c>
-      <c r="O13">
+      <c r="R13">
         <f t="shared" si="5"/>
-        <v>0.22889999999999999</v>
-      </c>
-      <c r="P13">
+        <v>0.2286</v>
+      </c>
+      <c r="S13">
+        <f t="shared" si="8"/>
+        <v>1836.1694659999998</v>
+      </c>
+      <c r="T13">
         <f t="shared" si="6"/>
-        <v>17.583194765000002</v>
-      </c>
-      <c r="Q13">
-        <f t="shared" si="7"/>
         <v>1.132E-4</v>
       </c>
-      <c r="R13">
-        <f t="shared" si="8"/>
-        <v>2.1338199999999999E-6</v>
-      </c>
-      <c r="T13" t="s">
-        <v>22</v>
-      </c>
-      <c r="U13" t="s">
-        <v>9</v>
-      </c>
-      <c r="V13" t="s">
-        <v>28</v>
+      <c r="U13" s="4">
+        <f>N13/1000 * Q13*T13</f>
+        <v>1.2802919999999999E-3</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>17</v>
+      </c>
+      <c r="Z13">
+        <v>1.132E-4</v>
       </c>
     </row>
     <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>26</v>
-      </c>
-      <c r="B14">
+        <v>23</v>
+      </c>
+      <c r="C14">
         <v>2350000</v>
       </c>
-      <c r="C14">
-        <v>6</v>
-      </c>
       <c r="D14">
-        <v>0.3</v>
+        <v>3.8</v>
       </c>
       <c r="E14">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="F14">
+        <v>0.30399999999999999</v>
+      </c>
+      <c r="G14">
         <f t="shared" si="0"/>
         <v>0.2</v>
       </c>
-      <c r="G14">
+      <c r="H14">
         <f t="shared" si="1"/>
         <v>0.25</v>
       </c>
-      <c r="H14">
+      <c r="I14">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="I14">
+      <c r="J14">
         <f t="shared" si="2"/>
         <v>0.2</v>
       </c>
-      <c r="J14">
+      <c r="K14">
         <f t="shared" si="3"/>
         <v>0.25</v>
       </c>
-      <c r="K14">
-        <v>11000</v>
-      </c>
       <c r="L14">
-        <v>3000</v>
+        <f t="shared" si="10"/>
+        <v>379.52500000000003</v>
       </c>
       <c r="M14">
-        <v>33000</v>
+        <v>200000</v>
       </c>
       <c r="N14">
+        <v>20000</v>
+      </c>
+      <c r="O14">
+        <v>200000</v>
+      </c>
+      <c r="P14" t="b">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="Q14">
         <f t="shared" si="4"/>
         <v>3.7699999999999997E-2</v>
       </c>
-      <c r="O14">
+      <c r="R14">
         <f t="shared" si="5"/>
-        <v>0.22889999999999999</v>
-      </c>
-      <c r="P14">
+        <v>0.2286</v>
+      </c>
+      <c r="S14">
+        <f t="shared" si="8"/>
+        <v>94.975999999999999</v>
+      </c>
+      <c r="T14">
         <f t="shared" si="6"/>
-        <v>612.04108858999996</v>
-      </c>
-      <c r="Q14">
-        <f t="shared" si="7"/>
         <v>1.132E-4</v>
       </c>
-      <c r="R14">
-        <f t="shared" si="8"/>
-        <v>1.280292E-5</v>
-      </c>
-      <c r="T14" t="s">
-        <v>23</v>
-      </c>
-      <c r="U14">
-        <v>0</v>
-      </c>
-      <c r="V14">
-        <v>0</v>
+      <c r="U14" s="4">
+        <f t="shared" si="9"/>
+        <v>8.5352800000000007E-5</v>
+      </c>
+      <c r="Y14" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z14">
+        <v>0.15</v>
       </c>
     </row>
     <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>27</v>
-      </c>
-      <c r="B15">
+        <v>24</v>
+      </c>
+      <c r="C15">
         <v>2350000</v>
       </c>
-      <c r="C15">
-        <v>0.9</v>
-      </c>
       <c r="D15">
-        <v>0.4</v>
+        <v>6</v>
       </c>
       <c r="E15">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="F15">
+        <v>0.48</v>
+      </c>
+      <c r="G15">
         <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
-      <c r="G15">
+      <c r="H15">
         <f t="shared" si="1"/>
         <v>0.25</v>
       </c>
-      <c r="H15">
+      <c r="I15">
         <v>0.1</v>
       </c>
-      <c r="I15">
+      <c r="J15">
         <f t="shared" si="2"/>
         <v>0.8</v>
       </c>
-      <c r="J15">
+      <c r="K15">
         <f t="shared" si="3"/>
         <v>0.25</v>
       </c>
-      <c r="K15">
-        <v>11000</v>
-      </c>
       <c r="L15">
-        <v>0</v>
+        <f t="shared" si="10"/>
+        <v>2312.3999999999996</v>
       </c>
       <c r="M15">
-        <v>33000</v>
+        <v>20000</v>
       </c>
       <c r="N15">
+        <v>20000</v>
+      </c>
+      <c r="O15">
+        <v>20000</v>
+      </c>
+      <c r="P15" t="b">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="Q15">
         <f t="shared" si="4"/>
         <v>3.7699999999999997E-2</v>
       </c>
-      <c r="O15">
+      <c r="R15">
         <f t="shared" si="5"/>
-        <v>0.22889999999999999</v>
-      </c>
-      <c r="P15">
+        <v>0.2286</v>
+      </c>
+      <c r="S15">
+        <f t="shared" si="8"/>
+        <v>2271.8683643999993</v>
+      </c>
+      <c r="T15">
         <f t="shared" si="6"/>
-        <v>303.85040000000009</v>
-      </c>
-      <c r="Q15">
+        <v>1.132E-4</v>
+      </c>
+      <c r="U15" s="4">
+        <f t="shared" si="9"/>
+        <v>8.5352800000000007E-5</v>
+      </c>
+      <c r="Y15" t="s">
+        <v>48</v>
+      </c>
+      <c r="Z15">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16">
+        <v>2350000</v>
+      </c>
+      <c r="D16">
+        <v>1.5</v>
+      </c>
+      <c r="E16">
+        <v>0.15</v>
+      </c>
+      <c r="F16">
+        <v>0.12</v>
+      </c>
+      <c r="G16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="I16">
+        <v>0.2</v>
+      </c>
+      <c r="J16">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="L16">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16">
+        <v>0</v>
+      </c>
+      <c r="O16">
+        <v>0</v>
+      </c>
+      <c r="P16" t="b">
         <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="Q16">
+        <f t="shared" si="4"/>
+        <v>3.7699999999999997E-2</v>
+      </c>
+      <c r="R16">
+        <f t="shared" si="5"/>
+        <v>0.2286</v>
+      </c>
+      <c r="S16">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T16">
+        <f t="shared" si="6"/>
         <v>1.132E-4</v>
       </c>
-      <c r="R15">
+      <c r="U16" s="4">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="Y16" t="s">
+        <v>50</v>
+      </c>
+      <c r="Z16">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="17" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>21</v>
+      </c>
+      <c r="C17">
+        <v>2350000</v>
+      </c>
+      <c r="D17">
+        <v>0.2</v>
+      </c>
+      <c r="E17">
+        <v>0.15</v>
+      </c>
+      <c r="F17">
+        <v>1.6E-2</v>
+      </c>
+      <c r="G17">
+        <f t="shared" si="0"/>
+        <v>0.3</v>
+      </c>
+      <c r="H17">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="I17">
+        <v>0.05</v>
+      </c>
+      <c r="J17">
+        <f t="shared" si="2"/>
+        <v>0.3</v>
+      </c>
+      <c r="K17">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="L17">
+        <f t="shared" si="10"/>
+        <v>30.667500000000004</v>
+      </c>
+      <c r="M17">
+        <v>20000</v>
+      </c>
+      <c r="N17">
+        <v>1000</v>
+      </c>
+      <c r="O17">
+        <v>20000</v>
+      </c>
+      <c r="P17" t="b">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="Q17">
+        <f t="shared" si="4"/>
+        <v>3.7699999999999997E-2</v>
+      </c>
+      <c r="R17">
+        <f t="shared" si="5"/>
+        <v>0.2286</v>
+      </c>
+      <c r="S17">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="T15" t="s">
+        <v>9.271466666666667</v>
+      </c>
+      <c r="T17">
+        <f t="shared" si="6"/>
+        <v>1.132E-4</v>
+      </c>
+      <c r="U17" s="4">
+        <f t="shared" si="9"/>
+        <v>4.2676399999999999E-6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>22</v>
+      </c>
+      <c r="C18">
+        <v>2350000</v>
+      </c>
+      <c r="D18">
+        <v>0.2</v>
+      </c>
+      <c r="E18">
+        <v>0.15</v>
+      </c>
+      <c r="F18">
+        <v>1.6E-2</v>
+      </c>
+      <c r="G18">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="H18">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="I18">
+        <v>0.2</v>
+      </c>
+      <c r="J18">
+        <f t="shared" si="2"/>
+        <v>0.8</v>
+      </c>
+      <c r="K18">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="L18">
+        <f t="shared" si="10"/>
+        <v>67.680000000000021</v>
+      </c>
+      <c r="M18">
+        <v>12345</v>
+      </c>
+      <c r="N18">
+        <v>73467</v>
+      </c>
+      <c r="O18">
+        <v>12345</v>
+      </c>
+      <c r="P18" t="b">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="Q18">
+        <f t="shared" si="4"/>
+        <v>3.7699999999999997E-2</v>
+      </c>
+      <c r="R18">
+        <f t="shared" si="5"/>
+        <v>0.2286</v>
+      </c>
+      <c r="S18">
+        <f t="shared" si="8"/>
+        <v>22.1965696</v>
+      </c>
+      <c r="T18">
+        <f t="shared" si="6"/>
+        <v>1.132E-4</v>
+      </c>
+      <c r="U18" s="4">
+        <f t="shared" si="9"/>
+        <v>3.1353070788000002E-4</v>
+      </c>
+      <c r="Y18" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z18" t="s">
+        <v>6</v>
+      </c>
+      <c r="AA18" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="19" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C19">
+        <v>2350000</v>
+      </c>
+      <c r="D19">
+        <v>0.9</v>
+      </c>
+      <c r="E19">
+        <v>0.15</v>
+      </c>
+      <c r="F19">
+        <v>7.2000000000000008E-2</v>
+      </c>
+      <c r="G19">
+        <f t="shared" si="0"/>
+        <v>0.2</v>
+      </c>
+      <c r="H19">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="I19">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="J19">
+        <f t="shared" si="2"/>
+        <v>0.2</v>
+      </c>
+      <c r="K19">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="L19">
+        <f t="shared" si="10"/>
+        <v>89.887500000000017</v>
+      </c>
+      <c r="M19">
+        <v>20000</v>
+      </c>
+      <c r="N19">
+        <v>20000</v>
+      </c>
+      <c r="O19">
+        <v>20000</v>
+      </c>
+      <c r="P19" t="b">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="Q19">
+        <f t="shared" si="4"/>
+        <v>3.7699999999999997E-2</v>
+      </c>
+      <c r="R19">
+        <f t="shared" si="5"/>
+        <v>0.2286</v>
+      </c>
+      <c r="S19">
+        <f t="shared" si="8"/>
+        <v>49.355864400000016</v>
+      </c>
+      <c r="T19">
+        <f t="shared" si="6"/>
+        <v>1.132E-4</v>
+      </c>
+      <c r="U19" s="4">
+        <f t="shared" si="9"/>
+        <v>8.5352800000000007E-5</v>
+      </c>
+      <c r="Y19" t="s">
+        <v>20</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+      <c r="AA19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
         <v>24</v>
       </c>
-      <c r="U15">
+      <c r="C20">
+        <v>2350000</v>
+      </c>
+      <c r="D20">
+        <v>0.4</v>
+      </c>
+      <c r="E20">
+        <v>0.15</v>
+      </c>
+      <c r="F20">
+        <v>3.2000000000000001E-2</v>
+      </c>
+      <c r="G20">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="H20">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="I20">
+        <v>0.1</v>
+      </c>
+      <c r="J20">
+        <f t="shared" si="2"/>
+        <v>0.8</v>
+      </c>
+      <c r="K20">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="L20">
+        <f t="shared" si="10"/>
+        <v>154.16000000000003</v>
+      </c>
+      <c r="M20">
+        <v>20000</v>
+      </c>
+      <c r="N20">
+        <v>20000</v>
+      </c>
+      <c r="O20">
+        <v>20000</v>
+      </c>
+      <c r="P20" t="b">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="Q20">
+        <f t="shared" si="4"/>
+        <v>3.7699999999999997E-2</v>
+      </c>
+      <c r="R20">
+        <f t="shared" si="5"/>
+        <v>0.2286</v>
+      </c>
+      <c r="S20">
+        <f t="shared" si="8"/>
+        <v>113.62836440000002</v>
+      </c>
+      <c r="T20">
+        <f t="shared" si="6"/>
+        <v>1.132E-4</v>
+      </c>
+      <c r="U20" s="4">
+        <f t="shared" si="9"/>
+        <v>8.5352800000000007E-5</v>
+      </c>
+      <c r="Y20" t="s">
+        <v>21</v>
+      </c>
+      <c r="Z20">
         <v>0.3</v>
       </c>
-      <c r="V15">
+      <c r="AA20">
         <v>0.3</v>
       </c>
     </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="T16" t="s">
-        <v>25</v>
-      </c>
-      <c r="U16">
+    <row r="21" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>20</v>
+      </c>
+      <c r="C21">
+        <v>2350000</v>
+      </c>
+      <c r="D21">
+        <v>6.1</v>
+      </c>
+      <c r="E21">
+        <v>0.15</v>
+      </c>
+      <c r="F21">
+        <v>0.48799999999999999</v>
+      </c>
+      <c r="G21">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="I21">
+        <v>0.2</v>
+      </c>
+      <c r="J21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="L21">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21">
+        <v>0</v>
+      </c>
+      <c r="O21">
+        <v>0</v>
+      </c>
+      <c r="P21" t="b">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="Q21">
+        <f t="shared" si="4"/>
+        <v>3.7699999999999997E-2</v>
+      </c>
+      <c r="R21">
+        <f t="shared" si="5"/>
+        <v>0.2286</v>
+      </c>
+      <c r="S21">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T21">
+        <f t="shared" si="6"/>
+        <v>1.132E-4</v>
+      </c>
+      <c r="U21" s="4">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="Y21" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z21">
         <v>0.8</v>
       </c>
-      <c r="V16">
+      <c r="AA21">
         <v>0.8</v>
       </c>
     </row>
-    <row r="17" spans="20:22" x14ac:dyDescent="0.2">
-      <c r="T17" t="s">
-        <v>26</v>
-      </c>
-      <c r="U17">
+    <row r="22" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>21</v>
+      </c>
+      <c r="C22">
+        <v>2350000</v>
+      </c>
+      <c r="D22">
+        <v>3.8</v>
+      </c>
+      <c r="E22">
+        <v>0.15</v>
+      </c>
+      <c r="F22">
+        <v>0.30399999999999999</v>
+      </c>
+      <c r="G22">
+        <f t="shared" si="0"/>
+        <v>0.3</v>
+      </c>
+      <c r="H22">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="I22">
         <v>0.2</v>
       </c>
-      <c r="V17">
+      <c r="J22">
+        <f t="shared" si="2"/>
+        <v>0.3</v>
+      </c>
+      <c r="K22">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="L22">
+        <f t="shared" si="10"/>
+        <v>482.22</v>
+      </c>
+      <c r="M22">
+        <v>123456</v>
+      </c>
+      <c r="N22">
+        <v>20000</v>
+      </c>
+      <c r="O22">
+        <v>234567</v>
+      </c>
+      <c r="P22" t="b">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="Q22">
+        <f t="shared" si="4"/>
+        <v>3.7699999999999997E-2</v>
+      </c>
+      <c r="R22">
+        <f t="shared" si="5"/>
+        <v>0.2286</v>
+      </c>
+      <c r="S22">
+        <f t="shared" si="8"/>
+        <v>225.94156120000002</v>
+      </c>
+      <c r="T22">
+        <f t="shared" si="6"/>
+        <v>1.132E-4</v>
+      </c>
+      <c r="U22" s="4">
+        <f t="shared" si="9"/>
+        <v>8.5352800000000007E-5</v>
+      </c>
+      <c r="Y22" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z22">
         <v>0.2</v>
       </c>
-    </row>
-    <row r="18" spans="20:22" x14ac:dyDescent="0.2">
-      <c r="T18" t="s">
-        <v>27</v>
-      </c>
-      <c r="U18">
+      <c r="AA22">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>22</v>
+      </c>
+      <c r="C23">
+        <v>2350000</v>
+      </c>
+      <c r="D23">
+        <v>6</v>
+      </c>
+      <c r="E23">
+        <v>0.15</v>
+      </c>
+      <c r="F23">
+        <v>0.48</v>
+      </c>
+      <c r="G23">
+        <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
-      <c r="V18">
+      <c r="H23">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="I23">
+        <v>0.05</v>
+      </c>
+      <c r="J23">
+        <f t="shared" si="2"/>
         <v>0.8</v>
+      </c>
+      <c r="K23">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="L23">
+        <f t="shared" si="10"/>
+        <v>2453.3999999999996</v>
+      </c>
+      <c r="M23">
+        <v>20000</v>
+      </c>
+      <c r="N23">
+        <v>20000</v>
+      </c>
+      <c r="O23">
+        <v>20000</v>
+      </c>
+      <c r="P23" t="b">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="Q23">
+        <f t="shared" si="4"/>
+        <v>3.7699999999999997E-2</v>
+      </c>
+      <c r="R23">
+        <f t="shared" si="5"/>
+        <v>0.2286</v>
+      </c>
+      <c r="S23">
+        <f t="shared" si="8"/>
+        <v>2412.8683643999993</v>
+      </c>
+      <c r="T23">
+        <f t="shared" si="6"/>
+        <v>1.132E-4</v>
+      </c>
+      <c r="U23" s="4">
+        <f t="shared" si="9"/>
+        <v>8.5352800000000007E-5</v>
+      </c>
+      <c r="Y23" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z23">
+        <v>0.8</v>
+      </c>
+      <c r="AA23">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="24" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>23</v>
+      </c>
+      <c r="C24">
+        <v>2350000</v>
+      </c>
+      <c r="D24">
+        <v>1.5</v>
+      </c>
+      <c r="E24">
+        <v>0.15</v>
+      </c>
+      <c r="F24">
+        <v>0.12</v>
+      </c>
+      <c r="G24">
+        <f t="shared" si="0"/>
+        <v>0.2</v>
+      </c>
+      <c r="H24">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="I24">
+        <v>0.2</v>
+      </c>
+      <c r="J24">
+        <f t="shared" si="2"/>
+        <v>0.2</v>
+      </c>
+      <c r="K24">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="L24">
+        <f t="shared" si="10"/>
+        <v>126.89999999999998</v>
+      </c>
+      <c r="M24">
+        <v>20000</v>
+      </c>
+      <c r="N24">
+        <v>20000</v>
+      </c>
+      <c r="O24">
+        <v>20000</v>
+      </c>
+      <c r="P24" t="b">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="Q24">
+        <f t="shared" si="4"/>
+        <v>3.7699999999999997E-2</v>
+      </c>
+      <c r="R24">
+        <f t="shared" si="5"/>
+        <v>0.2286</v>
+      </c>
+      <c r="S24">
+        <f t="shared" si="8"/>
+        <v>86.368364399999976</v>
+      </c>
+      <c r="T24">
+        <f t="shared" si="6"/>
+        <v>1.132E-4</v>
+      </c>
+      <c r="U24" s="4">
+        <f t="shared" si="9"/>
+        <v>8.5352800000000007E-5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>24</v>
+      </c>
+      <c r="C25">
+        <v>2350000</v>
+      </c>
+      <c r="D25">
+        <v>0.2</v>
+      </c>
+      <c r="E25">
+        <v>0.15</v>
+      </c>
+      <c r="F25">
+        <v>1.6E-2</v>
+      </c>
+      <c r="G25">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="H25">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="I25">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="J25">
+        <f t="shared" si="2"/>
+        <v>0.8</v>
+      </c>
+      <c r="K25">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="L25">
+        <f t="shared" si="10"/>
+        <v>79.90000000000002</v>
+      </c>
+      <c r="M25">
+        <v>20000</v>
+      </c>
+      <c r="N25">
+        <v>20000</v>
+      </c>
+      <c r="O25">
+        <v>20000</v>
+      </c>
+      <c r="P25" t="b">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="Q25">
+        <f t="shared" si="4"/>
+        <v>3.7699999999999997E-2</v>
+      </c>
+      <c r="R25">
+        <f t="shared" si="5"/>
+        <v>0.2286</v>
+      </c>
+      <c r="S25">
+        <f t="shared" si="8"/>
+        <v>39.368364400000019</v>
+      </c>
+      <c r="T25">
+        <f t="shared" si="6"/>
+        <v>1.132E-4</v>
+      </c>
+      <c r="U25" s="4">
+        <f t="shared" si="9"/>
+        <v>8.5352800000000007E-5</v>
+      </c>
+      <c r="Y25" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z25" t="s">
+        <v>37</v>
+      </c>
+      <c r="AA25" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="26" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>20</v>
+      </c>
+      <c r="C26">
+        <v>2350000</v>
+      </c>
+      <c r="D26">
+        <v>0.2</v>
+      </c>
+      <c r="E26">
+        <v>0.15</v>
+      </c>
+      <c r="F26">
+        <v>1.6E-2</v>
+      </c>
+      <c r="G26">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="I26">
+        <v>0.1</v>
+      </c>
+      <c r="J26">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="L26">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="M26">
+        <v>0</v>
+      </c>
+      <c r="N26">
+        <v>0</v>
+      </c>
+      <c r="O26">
+        <v>0</v>
+      </c>
+      <c r="P26" t="b">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="Q26">
+        <f t="shared" si="4"/>
+        <v>3.7699999999999997E-2</v>
+      </c>
+      <c r="R26">
+        <f t="shared" si="5"/>
+        <v>0.2286</v>
+      </c>
+      <c r="S26">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T26">
+        <f t="shared" si="6"/>
+        <v>1.132E-4</v>
+      </c>
+      <c r="U26" s="4">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="Y26" t="s">
+        <v>39</v>
+      </c>
+      <c r="Z26">
+        <v>0.9</v>
+      </c>
+      <c r="AA26">
+        <v>0.39800000000000002</v>
+      </c>
+    </row>
+    <row r="27" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="Y27" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z27">
+        <v>0.4</v>
+      </c>
+      <c r="AA27">
+        <v>0.54700000000000004</v>
+      </c>
+    </row>
+    <row r="28" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="Y28" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z28">
+        <v>6.1</v>
+      </c>
+      <c r="AA28">
+        <v>0.34799999999999998</v>
+      </c>
+    </row>
+    <row r="29" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="Y29" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z29">
+        <v>3.8</v>
+      </c>
+      <c r="AA29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="Y30" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z30">
+        <v>6</v>
+      </c>
+      <c r="AA30">
+        <v>0.72299999999999998</v>
+      </c>
+    </row>
+    <row r="31" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="Y31" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z31">
+        <v>1.5</v>
+      </c>
+      <c r="AA31">
+        <v>0.79600000000000004</v>
+      </c>
+    </row>
+    <row r="32" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="Y32" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z32">
+        <v>0.2</v>
+      </c>
+      <c r="AA32">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="33" spans="25:27" x14ac:dyDescent="0.2">
+      <c r="Y33" t="s">
+        <v>46</v>
+      </c>
+      <c r="Z33">
+        <v>0.2</v>
+      </c>
+      <c r="AA33">
+        <v>0.06</v>
       </c>
     </row>
   </sheetData>

--- a/packages/calculators/src/modules/test/11-wastewater.xlsx
+++ b/packages/calculators/src/modules/test/11-wastewater.xlsx
@@ -3,11 +3,6 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mackcheesman/Desktop/Work/EAP/Code/emissions-calculators-internal/packages/calculators/src/modules/test/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05701E81-48AA-EE4B-93F7-2376216C08ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>

--- a/packages/calculators/src/modules/test/11-wastewater.xlsx
+++ b/packages/calculators/src/modules/test/11-wastewater.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mackcheesman/Desktop/Work/EAP/Code/emissions-calculators-internal/packages/calculators/src/modules/test/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mackcheesman/Desktop/Work/EAP/Code/emissions-calculators/packages/calculators/src/modules/test/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05701E81-48AA-EE4B-93F7-2376216C08ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>

--- a/packages/calculators/src/modules/test/11-wastewater.xlsx
+++ b/packages/calculators/src/modules/test/11-wastewater.xlsx
@@ -3,11 +3,6 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mackcheesman/Desktop/Work/EAP/Code/emissions-calculators/packages/calculators/src/modules/test/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05701E81-48AA-EE4B-93F7-2376216C08ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
